--- a/docs/Requerimientos_Oasis.xlsx
+++ b/docs/Requerimientos_Oasis.xlsx
@@ -58,7 +58,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -81,12 +81,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00FFE699"/>
         <bgColor rgb="00FFE699"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FF9999"/>
-        <bgColor rgb="00FF9999"/>
       </patternFill>
     </fill>
     <fill>
@@ -134,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -163,9 +157,6 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -606,7 +597,7 @@
     <row r="13" ht="30" customHeight="1">
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>• Actualización 2026-07-19: se aplicaron correcciones sobre casi todos los hallazgos (marcadas '[Actualizado 2026-07-19]' en las notas), EXCEPTO 3 puntos clasificados como críticos que se dejaron sin tocar a propósito: el formulario público sin onSubmit funcional (RF-54/RF-55), el bug de 'devolver a empaque' en Express (RF-30) y las políticas RLS abiertas en tablas de negocio (RNF-02). Ver la hoja 'Deuda Técnica y Hallazgos' (columna Estado) para el detalle completo de qué se corrigió y qué sigue pendiente.</t>
+          <t>• Actualización 2026-07-19: se aplicaron correcciones sobre casi todos los hallazgos (marcadas '[Actualizado 2026-07-19]' en las notas), EXCEPTO 3 puntos clasificados como críticos que se dejaron sin tocar a propósito: el formulario público sin onSubmit funcional (RF-54/RF-55), el bug de 'devolver a empaque' en Express (RF-30) y las políticas RLS abiertas en tablas de negocio (RNF-02). El bug de RF-30 quedó corregido de todos modos el 2026-07-20, como efecto colateral de separar Express en su propia pantalla (no fue una tarea pedida). Los otros 2 puntos (formularios públicos y RLS abierta) siguen sin tocar a propósito. Ver la hoja 'Deuda Técnica y Hallazgos' (columna Estado) para el detalle completo.</t>
         </is>
       </c>
     </row>
@@ -628,7 +619,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G62"/>
+  <dimension ref="A1:G69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1750,14 +1741,14 @@
           <t>Alta</t>
         </is>
       </c>
-      <c r="F34" s="11" t="inlineStr">
-        <is>
-          <t>Roto</t>
+      <c r="F34" s="9" t="inlineStr">
+        <is>
+          <t>Implementado</t>
         </is>
       </c>
       <c r="G34" s="8" t="inlineStr">
         <is>
-          <t>La reversión de entrega dentro de la subvista Express falla por un error de referencia en el código (markPacked no se pasa como prop). No corregido a propósito en la pasada de mejoras del 2026-07-19 (clasificado como crítico, pendiente de abordar aparte).</t>
+          <t>Originalmente Roto: la reversión de entrega dentro de la subvista Express fallaba por un error de referencia en el código (markPacked no se pasaba como prop). No corregido a propósito en la pasada de mejoras del 2026-07-19 (clasificado como crítico). [Corregido de forma incidental, 2026-07-20] Al separar Express en su propia pantalla (/entregas/express) y extraer el pipeline compartido a KitchenPipeline.jsx + hooks/useOrderDayActions.js, la función ya queda correctamente en scope. No fue una tarea pedida — se resolvió como efecto colateral de la refactorización. Verificado con Playwright: se sembró una orden Express de prueba en estado DELIVERED, se confirmó que 'Devolver a empaque' la revierte a PACKED sin errores, y se limpiaron los datos de prueba.</t>
         </is>
       </c>
     </row>
@@ -1864,7 +1855,7 @@
       </c>
       <c r="G37" s="8" t="inlineStr">
         <is>
-          <t>Comparte el bug de RF-30.</t>
+          <t>[Actualizado 2026-07-20] El bug de RF-30 (que compartía) quedó corregido; ver RF-30 y RF-65 (pantalla propia /entregas/express).</t>
         </is>
       </c>
     </row>
@@ -2586,7 +2577,7 @@
           <t>Media</t>
         </is>
       </c>
-      <c r="F58" s="12" t="inlineStr">
+      <c r="F58" s="11" t="inlineStr">
         <is>
           <t>No implementado</t>
         </is>
@@ -2623,7 +2614,7 @@
           <t>Media</t>
         </is>
       </c>
-      <c r="F59" s="12" t="inlineStr">
+      <c r="F59" s="11" t="inlineStr">
         <is>
           <t>No implementado</t>
         </is>
@@ -2660,7 +2651,7 @@
           <t>Baja</t>
         </is>
       </c>
-      <c r="F60" s="12" t="inlineStr">
+      <c r="F60" s="11" t="inlineStr">
         <is>
           <t>No implementado</t>
         </is>
@@ -2742,6 +2733,265 @@
       <c r="G62" s="8" t="inlineStr">
         <is>
           <t>[Nuevo 2026-07-20, a petición del usuario] Columna closed_at (migración 20260720_close_monthly_payment.sql). Acción disponible solo desde Payments.jsx (Ingresos), no desde el detalle de cliente, a pedido explícito del usuario. Verificado con Playwright: se cerró un pago de prueba y se confirmó que deja de aparecer como 'disponible' en un pedido nuevo del mismo cliente; no se pudo probar el clic del botón en la UI real porque la cuenta de prueba no tiene rol Finanzas/Administrador (no se modificaron roles reales para evitar tocar permisos productivos).</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="8" t="inlineStr">
+        <is>
+          <t>RF-59</t>
+        </is>
+      </c>
+      <c r="B63" s="8" t="inlineStr">
+        <is>
+          <t>Combos</t>
+        </is>
+      </c>
+      <c r="C63" s="8" t="inlineStr">
+        <is>
+          <t>Gestionar catálogo de ítems de combo</t>
+        </is>
+      </c>
+      <c r="D63" s="8" t="inlineStr">
+        <is>
+          <t>El sistema debe permitir crear, editar y desactivar ítems de combo por categoría (Arroz, Proteína, Acompañamientos, Extras, Plato Extra), con porción fija en gramos para Arroz/Proteína y enlace opcional a una receta existente.</t>
+        </is>
+      </c>
+      <c r="E63" s="8" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="F63" s="9" t="inlineStr">
+        <is>
+          <t>Implementado</t>
+        </is>
+      </c>
+      <c r="G63" s="8" t="inlineStr">
+        <is>
+          <t>[Nuevo 2026-07-20, a petición del usuario] Página /combo-items (ComboItems.jsx + AddComboItem.jsx), enlace en el menú Gestión. Catálogo independiente de recipes, reutilizable entre semanas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="8" t="inlineStr">
+        <is>
+          <t>RF-60</t>
+        </is>
+      </c>
+      <c r="B64" s="8" t="inlineStr">
+        <is>
+          <t>Combos</t>
+        </is>
+      </c>
+      <c r="C64" s="8" t="inlineStr">
+        <is>
+          <t>Configurar el combo de la semana</t>
+        </is>
+      </c>
+      <c r="D64" s="8" t="inlineStr">
+        <is>
+          <t>El sistema debe permitir al administrador definir, para cada semana, el precio base del combo y —por categoría— qué ítems del catálogo están disponibles y cuántos puede elegir el cliente (máximo de selecciones). Para Plato Extra, además debe poder fijar el costo adicional de cada ítem elegido esa semana.</t>
+        </is>
+      </c>
+      <c r="E64" s="8" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="F64" s="9" t="inlineStr">
+        <is>
+          <t>Implementado</t>
+        </is>
+      </c>
+      <c r="G64" s="8" t="inlineStr">
+        <is>
+          <t>[Nuevo 2026-07-20] ComboWeekBuilder.jsx, accesible desde /combos. Tablas combo_weeks/combo_week_categories/combo_week_category_items. [Corregido 2026-07-20] El costo del Plato Extra es obligatorio (&gt;0) para cada ítem seleccionado — antes se guardaba silenciosamente como 0 si se dejaba vacío, lo que rompía el cálculo automático del precio final del pedido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="8" t="inlineStr">
+        <is>
+          <t>RF-61</t>
+        </is>
+      </c>
+      <c r="B65" s="8" t="inlineStr">
+        <is>
+          <t>Combos</t>
+        </is>
+      </c>
+      <c r="C65" s="8" t="inlineStr">
+        <is>
+          <t>Registrar pedido de combo de un cliente</t>
+        </is>
+      </c>
+      <c r="D65" s="8" t="inlineStr">
+        <is>
+          <t>El sistema debe permitir registrar el pedido de combo de un cliente contra el combo de la semana activo, respetando el máximo de selecciones por categoría, calculando el precio total (base + extras elegidos) y registrando el pago asociado (pendiente o pagado), con las mismas reglas de registro de pago que un pedido semanal normal.</t>
+        </is>
+      </c>
+      <c r="E65" s="8" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="F65" s="9" t="inlineStr">
+        <is>
+          <t>Implementado</t>
+        </is>
+      </c>
+      <c r="G65" s="8" t="inlineStr">
+        <is>
+          <t>[Nuevo 2026-07-20] AddComboOrder.jsx. payment_type='combo' en la tabla payments existente. [Confirmado 2026-07-20] Mismo patrón que orders/steps/StepPayment.jsx: Estado antes que Fecha, fecha visible/editable solo si 'Pagado', en blanco si 'Pendiente' hasta que se marque pagado (misma semántica que RF-57). Pedido puntual, sin recurrencia automática.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="8" t="inlineStr">
+        <is>
+          <t>RF-62</t>
+        </is>
+      </c>
+      <c r="B66" s="8" t="inlineStr">
+        <is>
+          <t>Combos</t>
+        </is>
+      </c>
+      <c r="C66" s="8" t="inlineStr">
+        <is>
+          <t>Seguimiento de entrega de combos (Cocina/Empaque/Entrega)</t>
+        </is>
+      </c>
+      <c r="D66" s="8" t="inlineStr">
+        <is>
+          <t>El sistema debe permitir dar seguimiento a los pedidos de combo a través de las mismas 3 etapas que el flujo semanal (Cocina, Empaque, Entrega), con transición a nivel de todo el pedido.</t>
+        </is>
+      </c>
+      <c r="E66" s="8" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="F66" s="9" t="inlineStr">
+        <is>
+          <t>Implementado</t>
+        </is>
+      </c>
+      <c r="G66" s="8" t="inlineStr">
+        <is>
+          <t>[Nuevo 2026-07-20] Pantalla propia /entregas/combos (DeliveriesCombos.jsx), componente ComboDeliveryView.jsx, con selector de semana. A diferencia del flujo semanal, la transición de estado es por pedido completo, no por plato individual. [Actualizado 2026-07-20] Se separó de una pestaña compartida con Cocina/Empaque/Entrega/Express a una pantalla propia (ver RF-65) tras detectar que las sub-pestañas internas se veían duplicadas respecto a la barra externa.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="8" t="inlineStr">
+        <is>
+          <t>RF-63</t>
+        </is>
+      </c>
+      <c r="B67" s="8" t="inlineStr">
+        <is>
+          <t>Combos</t>
+        </is>
+      </c>
+      <c r="C67" s="8" t="inlineStr">
+        <is>
+          <t>Vista agregada de producción por plato</t>
+        </is>
+      </c>
+      <c r="D67" s="8" t="inlineStr">
+        <is>
+          <t>El sistema debe poder mostrar, además de la vista por cliente, un resumen agregado por ítem de catálogo (ej. 'Arroz blanco: 3000 g', 'Ensalada: 4 unidades') sumando las selecciones de los pedidos de combo visibles en la etapa activa.</t>
+        </is>
+      </c>
+      <c r="E67" s="8" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="F67" s="9" t="inlineStr">
+        <is>
+          <t>Implementado</t>
+        </is>
+      </c>
+      <c r="G67" s="8" t="inlineStr">
+        <is>
+          <t>[Nuevo 2026-07-20] Selector 'Por cliente' / 'Por plato' dentro de /entregas/combos. Verificado con Playwright: la agregación suma correctamente porción fija × cantidad de selecciones.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="8" t="inlineStr">
+        <is>
+          <t>RF-64</t>
+        </is>
+      </c>
+      <c r="B68" s="8" t="inlineStr">
+        <is>
+          <t>Combos</t>
+        </is>
+      </c>
+      <c r="C68" s="8" t="inlineStr">
+        <is>
+          <t>Pantalla propia de Combos, separada de Pedidos, con vista Semana/Histórico</t>
+        </is>
+      </c>
+      <c r="D68" s="8" t="inlineStr">
+        <is>
+          <t>Los pedidos de combo deben gestionarse en una pantalla propia (no como pestaña de Pedidos), con las mismas dos vistas que Pedidos: Semana (combo vigente) e Histórico (semanas de combo anteriores, agrupadas y paginadas).</t>
+        </is>
+      </c>
+      <c r="E68" s="8" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="F68" s="9" t="inlineStr">
+        <is>
+          <t>Implementado</t>
+        </is>
+      </c>
+      <c r="G68" s="8" t="inlineStr">
+        <is>
+          <t>[Nuevo 2026-07-20, a petición del usuario] Ruta /combos (Combos.jsx), link propio en la navbar junto a Órdenes. 'Histórico' (ComboHistoryView.jsx) agrupa por combo_weeks y pagina de a 8, igual patrón que el Histórico de pedidos semanales. 'Actual' = combo_weeks más reciente por id; el resto es histórico. Verificado con Playwright: agrupado y tarjetas correctas con 2 semanas de prueba.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="8" t="inlineStr">
+        <is>
+          <t>RF-65</t>
+        </is>
+      </c>
+      <c r="B69" s="8" t="inlineStr">
+        <is>
+          <t>Recetas y Producción</t>
+        </is>
+      </c>
+      <c r="C69" s="8" t="inlineStr">
+        <is>
+          <t>Pantalla propia de Express, separada de Producción semanal</t>
+        </is>
+      </c>
+      <c r="D69" s="8" t="inlineStr">
+        <is>
+          <t>Los pedidos Express deben gestionarse en una pantalla propia dentro de Entregas (no como pestaña de la producción semanal).</t>
+        </is>
+      </c>
+      <c r="E69" s="8" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="F69" s="9" t="inlineStr">
+        <is>
+          <t>Implementado</t>
+        </is>
+      </c>
+      <c r="G69" s="8" t="inlineStr">
+        <is>
+          <t>[Nuevo 2026-07-20, a petición del usuario] Ruta /entregas/express (DeliveriesExpress.jsx). El dropdown 'Entregas' de la navbar agrupa ahora Producción/Express/Combos. Reutiliza el pipeline Cocina/Empaque/Entrega compartido (KitchenPipeline.jsx) y las transiciones de estado compartidas (hooks/useOrderDayActions.js), antes duplicadas entre la vista principal y la subvista Express.</t>
         </is>
       </c>
     </row>
@@ -2930,7 +3180,7 @@
           <t>Si en el futuro se habilita acceso de clientes finales al sistema, cada cliente debe ver únicamente sus propios datos.</t>
         </is>
       </c>
-      <c r="E8" s="13" t="inlineStr">
+      <c r="E8" s="12" t="inlineStr">
         <is>
           <t>Pendiente (recomendado)</t>
         </is>
@@ -3054,7 +3304,7 @@
           <t>La aplicación debe evitar pantallas en blanco ante errores inesperados de renderizado.</t>
         </is>
       </c>
-      <c r="E12" s="12" t="inlineStr">
+      <c r="E12" s="11" t="inlineStr">
         <is>
           <t>No implementado</t>
         </is>
@@ -3118,7 +3368,7 @@
           <t>Las reglas de negocio importantes (p. ej. tope de 4 pedidos por pago mensual) deben validarse también a nivel de base de datos.</t>
         </is>
       </c>
-      <c r="E14" s="12" t="inlineStr">
+      <c r="E14" s="11" t="inlineStr">
         <is>
           <t>No implementado</t>
         </is>
@@ -3598,7 +3848,7 @@
           <t>Las funciones que dependen de Supabase Edge Functions deben estar desplegadas y conectadas a la interfaz que las necesita.</t>
         </is>
       </c>
-      <c r="E29" s="12" t="inlineStr">
+      <c r="E29" s="11" t="inlineStr">
         <is>
           <t>No implementado</t>
         </is>
@@ -3699,9 +3949,9 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="12" t="inlineStr">
-        <is>
-          <t>Pendiente (crítico, a propósito)</t>
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>Corregido (incidental)</t>
         </is>
       </c>
       <c r="B6" s="8" t="inlineStr">
@@ -3711,17 +3961,17 @@
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>src/pages/Deliveries.jsx (subvista Express &gt; Entrega)</t>
+          <t>src/pages/DeliveriesExpress.jsx (antes: subvista Express de Deliveries.jsx)</t>
         </is>
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>'Devolver a empaque' llama a markPacked sin que esté disponible en el scope del componente ExpressView.</t>
+          <t>'Devolver a empaque' llamaba a markPacked sin que estuviera disponible en el scope del componente ExpressView. Quedó sin corregir a propósito el 2026-07-19 (clasificado crítico). El 2026-07-20, al separar Express en su propia pantalla y extraer el pipeline compartido a KitchenPipeline.jsx + hooks/useOrderDayActions.js (pedido no relacionado a este bug), la función quedó correctamente en scope.</t>
         </is>
       </c>
       <c r="E6" s="8" t="inlineStr">
         <is>
-          <t>Error en tiempo de ejecución al usar esa acción en pedidos Express.</t>
+          <t>Ya no falla. Verificado con Playwright con una orden Express de prueba sembrada directamente en la BD (no se pudo llegar a este estado por la UI real en el tiempo de la verificación): se confirmó la transición DELIVERED→PACKED sin errores de consola, y se limpiaron los datos de prueba.</t>
         </is>
       </c>
     </row>
@@ -3753,7 +4003,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="12" t="inlineStr">
+      <c r="A8" s="11" t="inlineStr">
         <is>
           <t>Pendiente (crítico, a propósito)</t>
         </is>
@@ -4104,7 +4354,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="14" t="inlineStr">
+      <c r="A21" s="13" t="inlineStr">
         <is>
           <t>Revertido</t>
         </is>

--- a/docs/Requerimientos_Oasis.xlsx
+++ b/docs/Requerimientos_Oasis.xlsx
@@ -619,7 +619,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G69"/>
+  <dimension ref="A1:G70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2992,6 +2992,43 @@
       <c r="G69" s="8" t="inlineStr">
         <is>
           <t>[Nuevo 2026-07-20, a petición del usuario] Ruta /entregas/express (DeliveriesExpress.jsx). El dropdown 'Entregas' de la navbar agrupa ahora Producción/Express/Combos. Reutiliza el pipeline Cocina/Empaque/Entrega compartido (KitchenPipeline.jsx) y las transiciones de estado compartidas (hooks/useOrderDayActions.js), antes duplicadas entre la vista principal y la subvista Express.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="8" t="inlineStr">
+        <is>
+          <t>RF-66</t>
+        </is>
+      </c>
+      <c r="B70" s="8" t="inlineStr">
+        <is>
+          <t>Combos</t>
+        </is>
+      </c>
+      <c r="C70" s="8" t="inlineStr">
+        <is>
+          <t>Permitir exceder el máximo de selecciones cobrando un extra</t>
+        </is>
+      </c>
+      <c r="D70" s="8" t="inlineStr">
+        <is>
+          <t>El sistema debe permitir que, al registrar un pedido de combo, el cliente elija un mismo ítem más de una vez (ej. 2 unidades de un acompañamiento si el combo da 2 cupos de esa categoría) y, una vez agotado el máximo de selecciones configurado para su categoría en el combo de la semana, siga agregando unidades adicionales del mismo o de otros ítems. Cada unidad que exceda ese máximo se debe poder agregar igualmente al pedido, registrándose como un extra: el sistema debe avisar que la selección adicional se cobrará aparte y solicitar el monto a cobrar por esa unidad extra, permitiendo agregar varias unidades extra (no solo una) y con un monto distinto por cada una si hace falta. El monto de los extras se debe sumar al precio total del pedido.</t>
+        </is>
+      </c>
+      <c r="E70" s="8" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="F70" s="9" t="inlineStr">
+        <is>
+          <t>Implementado</t>
+        </is>
+      </c>
+      <c r="G70" s="8" t="inlineStr">
+        <is>
+          <t>[Nuevo 2026-07-31, a petición del usuario] Implementado con un modelo de cantidades (no on/off): cada ítem tiene un stepper +/- (ComboCategorySelector.jsx) en vez de un checkbox, así que puede elegirse el mismo ítem varias veces. Al llegar al máximo configurado (de su categoría o del pool Arroz/Proteína/Acompañamiento/Extra), cada nueva unidad abre un modal (ComboExtraChargeModal.jsx) que avisa que es un extra y pide su precio, precargado con el último monto usado para ese ítem — se puede repetir para agregar tantas unidades extra como haga falta, del mismo ítem o de varios, cada una con su propio precio. Lógica de cantidades/extras centralizada en el hook useComboSelections.js (src/hooks); cada unidad se persiste como una fila propia en combo_order_selections (is_extra/extra_charge, migración 20260731_combo_order_selections_extra.sql — mismo criterio que ya usa aggregateComboSelections para contar producción, sin necesidad de columna de cantidad). El precio total (computeComboPrice) y los resúmenes (paso de confirmación, ComboOrderCard) agrupan esas filas por ítem con groupSelectionsByItem para mostrar 'Ítem ×N' y el desglose de extras. Pendiente de aplicar en la base de datos real: la migración SQL no se ejecutó contra Supabase en esta sesión (no había credenciales/CLI vinculado disponibles). No se pudo probar end-to-end con Playwright contra el entorno real por la misma razón — sí se verificó que build y lint pasan sin errores nuevos.</t>
         </is>
       </c>
     </row>

--- a/docs/Requerimientos_Oasis.xlsx
+++ b/docs/Requerimientos_Oasis.xlsx
@@ -619,7 +619,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G70"/>
+  <dimension ref="A1:G71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2232,7 +2232,11 @@
           <t>Implementado</t>
         </is>
       </c>
-      <c r="G48" s="8" t="inlineStr"/>
+      <c r="G48" s="8" t="inlineStr">
+        <is>
+          <t>[Actualizado 2026-08-17, a petición del usuario] Se reordenó la jerarquía de filtros: Cliente y Tipo de pago ahora son el filtro principal, mostrado por encima de las pestañas de fecha (antes al revés). Se agregó una pestaña 'Hoy' (antes solo Esta Semana/Historial), quedando Hoy / Esta Semana / Historial / Estadísticas. Ver también RF-67 (filtro de mensuales vigentes).</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="8" t="inlineStr">
@@ -3029,6 +3033,43 @@
       <c r="G70" s="8" t="inlineStr">
         <is>
           <t>[Nuevo 2026-07-31, a petición del usuario] Implementado con un modelo de cantidades (no on/off): cada ítem tiene un stepper +/- (ComboCategorySelector.jsx) en vez de un checkbox, así que puede elegirse el mismo ítem varias veces. Al llegar al máximo configurado (de su categoría o del pool Arroz/Proteína/Acompañamiento/Extra), cada nueva unidad abre un modal (ComboExtraChargeModal.jsx) que avisa que es un extra y pide su precio, precargado con el último monto usado para ese ítem — se puede repetir para agregar tantas unidades extra como haga falta, del mismo ítem o de varios, cada una con su propio precio. Lógica de cantidades/extras centralizada en el hook useComboSelections.js (src/hooks); cada unidad se persiste como una fila propia en combo_order_selections (is_extra/extra_charge, migración 20260731_combo_order_selections_extra.sql — mismo criterio que ya usa aggregateComboSelections para contar producción, sin necesidad de columna de cantidad). El precio total (computeComboPrice) y los resúmenes (paso de confirmación, ComboOrderCard) agrupan esas filas por ítem con groupSelectionsByItem para mostrar 'Ítem ×N' y el desglose de extras. Pendiente de aplicar en la base de datos real: la migración SQL no se ejecutó contra Supabase en esta sesión (no había credenciales/CLI vinculado disponibles). No se pudo probar end-to-end con Playwright contra el entorno real por la misma razón — sí se verificó que build y lint pasan sin errores nuevos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="8" t="inlineStr">
+        <is>
+          <t>RF-67</t>
+        </is>
+      </c>
+      <c r="B71" s="8" t="inlineStr">
+        <is>
+          <t>Pagos y Facturación</t>
+        </is>
+      </c>
+      <c r="C71" s="8" t="inlineStr">
+        <is>
+          <t>Filtrar pagos mensuales vigentes con cupo disponible</t>
+        </is>
+      </c>
+      <c r="D71" s="8" t="inlineStr">
+        <is>
+          <t>Al filtrar Ingresos por Tipo de pago = 'Mensual', el sistema debe mostrar únicamente los pagos mensuales vigentes (no cerrados manualmente, no cancelados) que todavía tienen cupo (menos de 4 órdenes vinculadas) — el mismo criterio de elegibilidad que usa el asistente de pedidos para ofrecer un pago reutilizable — en vez de listar también los ya completos, cerrados o cancelados.</t>
+        </is>
+      </c>
+      <c r="E71" s="8" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="F71" s="9" t="inlineStr">
+        <is>
+          <t>Implementado</t>
+        </is>
+      </c>
+      <c r="G71" s="8" t="inlineStr">
+        <is>
+          <t>[Nuevo 2026-08-17, a petición del usuario] Payments.jsx: filtro de Tipo de pago, al valor 'monthly', además de igualar payment_type aplica status in (pending, paid) AND closed_at IS NULL AND órdenes vinculadas &lt; 4, con un badge visible ('Mostrando solo mensuales vigentes con órdenes disponibles'). Pensado para auditar de un vistazo cuál es el pago mensual activo de cada cliente y detectar fragmentación (más de un pago vigente simultáneo para el mismo cliente) sin consultar la base de datos directamente — ver project-monthly-payment-fragmentation en memoria. Verificado con Playwright contra producción: con este filtro + pestaña Historial se confirmaron 11 pagos mensuales vigentes, uno por cliente, sin duplicados; el filtro destapó un pago suelto real (Erick Vásquez #19, 2/4, de junio) que se había quedado sin cerrar en una limpieza de datos anterior — se cerró en el momento.</t>
         </is>
       </c>
     </row>
